--- a/public/sap-reporting/expansion-150-downloads/EXT-QM08-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-QM08-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R59c9a73823534e5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rfd925fa53b2e4ea5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R2f7ebdd001384131"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R0f92276f9c4243ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R0919ba6680f14c43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R451073a6fbe24761"/>
   </x:sheets>
 </x:workbook>
 </file>
